--- a/data/contratos.xlsx
+++ b/data/contratos.xlsx
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
